--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:07</t>
+    <t xml:space="preserve">2026-09-09 22:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:04</t>
+    <t xml:space="preserve">2026-09-17 13:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,26 +955,26 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>393130.56</v>
+        <v>439330.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>333510.84</v>
+        <v>393130.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>439330.41</v>
+        <v>333510.84</v>
       </c>
     </row>
     <row r="5">
@@ -1015,101 +1015,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>352166.28</v>
+        <v>399113.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>393130.56</v>
+        <v>439330.41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>409295.44</v>
+        <v>466621.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>299927.28</v>
+        <v>352166.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>333510.84</v>
+        <v>393130.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>362494.78</v>
+        <v>409295.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>399113.84</v>
+        <v>299927.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>439330.41</v>
+        <v>333510.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>466621.78</v>
+        <v>362494.78</v>
       </c>
     </row>
     <row r="11">

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:35</t>
+    <t xml:space="preserve">2026-09-25 21:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -573,7 +573,7 @@
         <v>253344.16</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15477.65</v>
+        <v>15477.66</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>6.11</v>
@@ -665,7 +665,7 @@
         <v>305889.41</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>37235.87</v>
+        <v>37235.88</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>12.17</v>
@@ -780,7 +780,7 @@
         <v>368403.69</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37475.9</v>
+        <v>37475.91</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>10.17</v>
@@ -803,7 +803,7 @@
         <v>380552.91</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>41070.15</v>
+        <v>41070.16</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>10.79</v>
@@ -849,7 +849,7 @@
         <v>399113.84</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>40216.57</v>
+        <v>40216.56</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>10.08</v>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_aysen.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:36</t>
+    <t xml:space="preserve">2026-10-05 07:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
